--- a/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0671 - Mulholland Grey.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0671 - Mulholland Grey.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\H&amp;M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C360A7-8779-43A3-B21B-DC1DD694B161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3356A253-7BBE-4892-BC54-504EB0D4087C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A072BB5A-5EDC-484C-BA84-6A4DA20DDBC1}"/>
   </bookViews>
@@ -2212,6 +2212,321 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="71" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="67" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="5" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="5" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="66" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="66" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="10" borderId="69" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="10" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="10" borderId="71" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="68" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="71" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2227,12 +2542,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -2310,315 +2619,6 @@
     <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="66" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="66" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="10" borderId="69" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="10" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="10" borderId="71" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="68" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="71" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="67" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="5" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="5" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="52" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4041,21 +4041,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="189">
+      <c r="C2" s="284">
         <v>46284</v>
       </c>
-      <c r="D2" s="190"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="189" t="s">
+      <c r="D2" s="285"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="190"/>
-      <c r="H2" s="192" t="s">
+      <c r="G2" s="285"/>
+      <c r="H2" s="287" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="193"/>
-      <c r="J2" s="193"/>
-      <c r="K2" s="194"/>
+      <c r="I2" s="288"/>
+      <c r="J2" s="288"/>
+      <c r="K2" s="289"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -4064,17 +4064,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="189" t="s">
+      <c r="C3" s="284" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="190"/>
-      <c r="E3" s="191"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="201" t="s">
+      <c r="D3" s="285"/>
+      <c r="E3" s="286"/>
+      <c r="F3" s="290"/>
+      <c r="G3" s="291"/>
+      <c r="H3" s="296" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="202"/>
+      <c r="I3" s="297"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -4088,17 +4088,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="298" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="204"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="198"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="206"/>
-      <c r="K4" s="207"/>
+      <c r="D4" s="299"/>
+      <c r="E4" s="300"/>
+      <c r="F4" s="292"/>
+      <c r="G4" s="293"/>
+      <c r="H4" s="301"/>
+      <c r="I4" s="302"/>
+      <c r="J4" s="301"/>
+      <c r="K4" s="302"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -4107,17 +4107,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="208">
+      <c r="C5" s="303">
         <v>512241934</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="210"/>
-      <c r="F5" s="197"/>
-      <c r="G5" s="198"/>
-      <c r="H5" s="187"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="187"/>
-      <c r="K5" s="188"/>
+      <c r="D5" s="304"/>
+      <c r="E5" s="305"/>
+      <c r="F5" s="292"/>
+      <c r="G5" s="293"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="267"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -4126,17 +4126,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="211" t="s">
+      <c r="C6" s="274" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="212"/>
-      <c r="E6" s="213"/>
-      <c r="F6" s="197"/>
-      <c r="G6" s="198"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="187"/>
-      <c r="K6" s="188"/>
+      <c r="D6" s="275"/>
+      <c r="E6" s="276"/>
+      <c r="F6" s="292"/>
+      <c r="G6" s="293"/>
+      <c r="H6" s="266"/>
+      <c r="I6" s="267"/>
+      <c r="J6" s="266"/>
+      <c r="K6" s="267"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -4145,17 +4145,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="184" t="s">
+      <c r="C7" s="281" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="185"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="197"/>
-      <c r="G7" s="198"/>
-      <c r="H7" s="187"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="187"/>
-      <c r="K7" s="188"/>
+      <c r="D7" s="282"/>
+      <c r="E7" s="283"/>
+      <c r="F7" s="292"/>
+      <c r="G7" s="293"/>
+      <c r="H7" s="266"/>
+      <c r="I7" s="267"/>
+      <c r="J7" s="266"/>
+      <c r="K7" s="267"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -4164,15 +4164,15 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="214"/>
-      <c r="D8" s="215"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="197"/>
-      <c r="G8" s="198"/>
+      <c r="C8" s="277"/>
+      <c r="D8" s="278"/>
+      <c r="E8" s="279"/>
+      <c r="F8" s="292"/>
+      <c r="G8" s="293"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="187"/>
-      <c r="K8" s="188"/>
+      <c r="J8" s="266"/>
+      <c r="K8" s="267"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -4181,17 +4181,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="217">
+      <c r="C9" s="271">
         <v>6</v>
       </c>
-      <c r="D9" s="218"/>
-      <c r="E9" s="219"/>
-      <c r="F9" s="197"/>
-      <c r="G9" s="198"/>
+      <c r="D9" s="272"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="292"/>
+      <c r="G9" s="293"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="187"/>
-      <c r="K9" s="188"/>
+      <c r="J9" s="266"/>
+      <c r="K9" s="267"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -4200,15 +4200,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="217"/>
-      <c r="D10" s="218"/>
-      <c r="E10" s="219"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="198"/>
+      <c r="C10" s="271"/>
+      <c r="D10" s="272"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="292"/>
+      <c r="G10" s="293"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="188"/>
+      <c r="J10" s="266"/>
+      <c r="K10" s="267"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -4217,15 +4217,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="220"/>
-      <c r="D11" s="221"/>
-      <c r="E11" s="222"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="198"/>
-      <c r="H11" s="187"/>
-      <c r="I11" s="188"/>
-      <c r="J11" s="187"/>
-      <c r="K11" s="188"/>
+      <c r="C11" s="268"/>
+      <c r="D11" s="269"/>
+      <c r="E11" s="270"/>
+      <c r="F11" s="292"/>
+      <c r="G11" s="293"/>
+      <c r="H11" s="266"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="266"/>
+      <c r="K11" s="267"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -4234,17 +4234,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="223" t="s">
+      <c r="C12" s="263" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="224"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="197"/>
-      <c r="G12" s="198"/>
-      <c r="H12" s="187"/>
-      <c r="I12" s="188"/>
-      <c r="J12" s="187"/>
-      <c r="K12" s="188"/>
+      <c r="D12" s="264"/>
+      <c r="E12" s="265"/>
+      <c r="F12" s="292"/>
+      <c r="G12" s="293"/>
+      <c r="H12" s="266"/>
+      <c r="I12" s="267"/>
+      <c r="J12" s="266"/>
+      <c r="K12" s="267"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -4253,15 +4253,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="220"/>
-      <c r="D13" s="221"/>
-      <c r="E13" s="222"/>
-      <c r="F13" s="199"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="187"/>
-      <c r="I13" s="188"/>
-      <c r="J13" s="187"/>
-      <c r="K13" s="188"/>
+      <c r="C13" s="268"/>
+      <c r="D13" s="269"/>
+      <c r="E13" s="270"/>
+      <c r="F13" s="294"/>
+      <c r="G13" s="295"/>
+      <c r="H13" s="266"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="266"/>
+      <c r="K13" s="267"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -4270,17 +4270,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="226"/>
-      <c r="D14" s="226"/>
-      <c r="E14" s="227"/>
-      <c r="F14" s="228" t="s">
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="250"/>
+      <c r="F14" s="251" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="229"/>
-      <c r="H14" s="232" t="s">
+      <c r="G14" s="252"/>
+      <c r="H14" s="255" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="233"/>
+      <c r="I14" s="256"/>
       <c r="J14" s="17"/>
       <c r="K14" s="18"/>
       <c r="L14" s="4"/>
@@ -4298,14 +4298,14 @@
       <c r="E15" s="16">
         <v>1</v>
       </c>
-      <c r="F15" s="230"/>
-      <c r="G15" s="231"/>
-      <c r="H15" s="230"/>
-      <c r="I15" s="234"/>
-      <c r="J15" s="235" t="s">
+      <c r="F15" s="253"/>
+      <c r="G15" s="254"/>
+      <c r="H15" s="253"/>
+      <c r="I15" s="257"/>
+      <c r="J15" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="237" t="s">
+      <c r="K15" s="260" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -4331,12 +4331,12 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="239" t="s">
+      <c r="H16" s="262" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="239"/>
-      <c r="J16" s="236"/>
-      <c r="K16" s="238"/>
+      <c r="I16" s="262"/>
+      <c r="J16" s="259"/>
+      <c r="K16" s="261"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
@@ -4362,15 +4362,15 @@
       <c r="B18" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="241" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="242"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="242"/>
+      <c r="G18" s="242"/>
+      <c r="H18" s="242"/>
+      <c r="I18" s="243"/>
       <c r="J18" s="28"/>
       <c r="K18" s="29"/>
       <c r="L18" s="25"/>
@@ -4413,13 +4413,13 @@
     <row r="21" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A21" s="26"/>
       <c r="B21" s="93"/>
-      <c r="C21" s="243"/>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-      <c r="G21" s="244"/>
-      <c r="H21" s="244"/>
-      <c r="I21" s="245"/>
+      <c r="C21" s="244"/>
+      <c r="D21" s="245"/>
+      <c r="E21" s="245"/>
+      <c r="F21" s="245"/>
+      <c r="G21" s="245"/>
+      <c r="H21" s="245"/>
+      <c r="I21" s="246"/>
       <c r="J21" s="94"/>
       <c r="K21" s="95"/>
       <c r="L21" s="25"/>
@@ -4445,10 +4445,10 @@
       <c r="G22" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="246" t="s">
+      <c r="H22" s="237" t="s">
         <v>38</v>
       </c>
-      <c r="I22" s="247"/>
+      <c r="I22" s="238"/>
       <c r="J22" s="99"/>
       <c r="K22" s="100"/>
       <c r="L22" s="25"/>
@@ -4466,10 +4466,10 @@
       <c r="G23" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="248" t="s">
+      <c r="H23" s="239" t="s">
         <v>39</v>
       </c>
-      <c r="I23" s="249"/>
+      <c r="I23" s="240"/>
       <c r="J23" s="99"/>
       <c r="K23" s="100"/>
       <c r="L23" s="25"/>
@@ -4502,8 +4502,8 @@
       <c r="E25" s="97"/>
       <c r="F25" s="97"/>
       <c r="G25" s="97"/>
-      <c r="H25" s="250"/>
-      <c r="I25" s="251"/>
+      <c r="H25" s="247"/>
+      <c r="I25" s="248"/>
       <c r="J25" s="99"/>
       <c r="K25" s="100"/>
       <c r="L25" s="25"/>
@@ -4519,8 +4519,8 @@
       <c r="E26" s="97"/>
       <c r="F26" s="102"/>
       <c r="G26" s="102"/>
-      <c r="H26" s="252"/>
-      <c r="I26" s="252"/>
+      <c r="H26" s="227"/>
+      <c r="I26" s="227"/>
       <c r="J26" s="99"/>
       <c r="K26" s="100"/>
       <c r="L26" s="25"/>
@@ -4529,13 +4529,13 @@
     <row r="27" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A27" s="26"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="256"/>
-      <c r="D27" s="257"/>
-      <c r="E27" s="257"/>
-      <c r="F27" s="257"/>
-      <c r="G27" s="257"/>
-      <c r="H27" s="257"/>
-      <c r="I27" s="258"/>
+      <c r="C27" s="231"/>
+      <c r="D27" s="232"/>
+      <c r="E27" s="232"/>
+      <c r="F27" s="232"/>
+      <c r="G27" s="232"/>
+      <c r="H27" s="232"/>
+      <c r="I27" s="233"/>
       <c r="J27" s="38"/>
       <c r="K27" s="39"/>
       <c r="L27" s="25"/>
@@ -4557,10 +4557,10 @@
       <c r="G28" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="252" t="s">
+      <c r="H28" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="252"/>
+      <c r="I28" s="227"/>
       <c r="J28" s="99"/>
       <c r="K28" s="100"/>
       <c r="L28" s="25"/>
@@ -4618,8 +4618,8 @@
       <c r="E31" s="97"/>
       <c r="F31" s="109"/>
       <c r="G31" s="109"/>
-      <c r="H31" s="253"/>
-      <c r="I31" s="254"/>
+      <c r="H31" s="228"/>
+      <c r="I31" s="229"/>
       <c r="J31" s="109"/>
       <c r="K31" s="109"/>
       <c r="L31" s="25"/>
@@ -4629,10 +4629,10 @@
       <c r="A32" s="26"/>
       <c r="B32" s="110"/>
       <c r="C32" s="111"/>
-      <c r="D32" s="259"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="260"/>
-      <c r="G32" s="261"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="235"/>
+      <c r="F32" s="235"/>
+      <c r="G32" s="236"/>
       <c r="H32" s="112"/>
       <c r="I32" s="113"/>
       <c r="J32" s="114"/>
@@ -4660,10 +4660,10 @@
       <c r="G33" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="H33" s="246" t="s">
+      <c r="H33" s="237" t="s">
         <v>38</v>
       </c>
-      <c r="I33" s="247"/>
+      <c r="I33" s="238"/>
       <c r="J33" s="116"/>
       <c r="K33" s="42"/>
       <c r="L33" s="25"/>
@@ -4681,10 +4681,10 @@
       <c r="G34" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="248" t="s">
+      <c r="H34" s="239" t="s">
         <v>39</v>
       </c>
-      <c r="I34" s="249"/>
+      <c r="I34" s="240"/>
       <c r="J34" s="116"/>
       <c r="K34" s="42"/>
       <c r="L34" s="25"/>
@@ -4723,10 +4723,10 @@
       <c r="G36" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="H36" s="255" t="s">
+      <c r="H36" s="230" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="255"/>
+      <c r="I36" s="230"/>
       <c r="J36" s="100"/>
       <c r="K36" s="100"/>
       <c r="L36" s="25"/>
@@ -4750,10 +4750,10 @@
       <c r="G37" s="100" t="s">
         <v>50</v>
       </c>
-      <c r="H37" s="262" t="s">
+      <c r="H37" s="213" t="s">
         <v>54</v>
       </c>
-      <c r="I37" s="262"/>
+      <c r="I37" s="213"/>
       <c r="J37" s="100"/>
       <c r="K37" s="100"/>
       <c r="L37" s="25"/>
@@ -4781,15 +4781,15 @@
       <c r="B39" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="263" t="s">
+      <c r="C39" s="214" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="264"/>
-      <c r="E39" s="264"/>
-      <c r="F39" s="264"/>
-      <c r="G39" s="265"/>
-      <c r="H39" s="267"/>
-      <c r="I39" s="268"/>
+      <c r="D39" s="215"/>
+      <c r="E39" s="215"/>
+      <c r="F39" s="215"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="209"/>
+      <c r="I39" s="210"/>
       <c r="J39" s="123"/>
       <c r="K39" s="123"/>
       <c r="L39" s="25"/>
@@ -4809,10 +4809,10 @@
       <c r="G40" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="H40" s="269" t="s">
+      <c r="H40" s="211" t="s">
         <v>58</v>
       </c>
-      <c r="I40" s="270"/>
+      <c r="I40" s="212"/>
       <c r="J40" s="126"/>
       <c r="K40" s="126"/>
       <c r="L40" s="25"/>
@@ -4830,10 +4830,10 @@
       <c r="G41" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="H41" s="269" t="s">
+      <c r="H41" s="211" t="s">
         <v>59</v>
       </c>
-      <c r="I41" s="270"/>
+      <c r="I41" s="212"/>
       <c r="J41" s="126"/>
       <c r="K41" s="126"/>
       <c r="L41" s="25"/>
@@ -4842,12 +4842,12 @@
     <row r="42" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A42" s="26"/>
       <c r="B42" s="169"/>
-      <c r="C42" s="273" t="s">
+      <c r="C42" s="220" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="274"/>
-      <c r="E42" s="274"/>
-      <c r="F42" s="275"/>
+      <c r="D42" s="221"/>
+      <c r="E42" s="221"/>
+      <c r="F42" s="222"/>
       <c r="G42" s="170"/>
       <c r="H42" s="171"/>
       <c r="I42" s="172"/>
@@ -4872,10 +4872,10 @@
       <c r="G43" s="176" t="s">
         <v>50</v>
       </c>
-      <c r="H43" s="276" t="s">
+      <c r="H43" s="223" t="s">
         <v>58</v>
       </c>
-      <c r="I43" s="276"/>
+      <c r="I43" s="223"/>
       <c r="J43" s="167"/>
       <c r="K43" s="168"/>
       <c r="L43" s="25"/>
@@ -4893,10 +4893,10 @@
       <c r="G44" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="H44" s="277" t="s">
+      <c r="H44" s="224" t="s">
         <v>76</v>
       </c>
-      <c r="I44" s="277"/>
+      <c r="I44" s="224"/>
       <c r="J44" s="167"/>
       <c r="K44" s="168"/>
       <c r="L44" s="25"/>
@@ -4914,10 +4914,10 @@
       <c r="G45" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="H45" s="278" t="s">
+      <c r="H45" s="225" t="s">
         <v>59</v>
       </c>
-      <c r="I45" s="279"/>
+      <c r="I45" s="226"/>
       <c r="J45" s="167"/>
       <c r="K45" s="168"/>
       <c r="L45" s="25"/>
@@ -4956,10 +4956,10 @@
       <c r="G47" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="H47" s="271" t="s">
+      <c r="H47" s="218" t="s">
         <v>61</v>
       </c>
-      <c r="I47" s="272"/>
+      <c r="I47" s="219"/>
       <c r="J47" s="100"/>
       <c r="K47" s="100"/>
       <c r="L47" s="25"/>
@@ -4981,8 +4981,8 @@
       </c>
       <c r="F48" s="109"/>
       <c r="G48" s="109"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
+      <c r="H48" s="217"/>
+      <c r="I48" s="217"/>
       <c r="J48" s="138"/>
       <c r="K48" s="138"/>
       <c r="L48" s="25"/>
@@ -5023,10 +5023,10 @@
       <c r="G50" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="H50" s="281" t="s">
+      <c r="H50" s="202" t="s">
         <v>64</v>
       </c>
-      <c r="I50" s="281"/>
+      <c r="I50" s="202"/>
       <c r="J50" s="138"/>
       <c r="K50" s="138"/>
       <c r="L50" s="25"/>
@@ -5044,10 +5044,10 @@
       <c r="G51" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="H51" s="282" t="s">
+      <c r="H51" s="203" t="s">
         <v>65</v>
       </c>
-      <c r="I51" s="282"/>
+      <c r="I51" s="203"/>
       <c r="J51" s="138"/>
       <c r="K51" s="138"/>
       <c r="L51" s="25"/>
@@ -5067,8 +5067,8 @@
       <c r="E52" s="97"/>
       <c r="F52" s="100"/>
       <c r="G52" s="100"/>
-      <c r="H52" s="283"/>
-      <c r="I52" s="283"/>
+      <c r="H52" s="204"/>
+      <c r="I52" s="204"/>
       <c r="J52" s="100"/>
       <c r="K52" s="100"/>
       <c r="L52" s="25"/>
@@ -5077,13 +5077,13 @@
     <row r="53" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A53" s="26"/>
       <c r="B53" s="110"/>
-      <c r="C53" s="285"/>
-      <c r="D53" s="286"/>
-      <c r="E53" s="286"/>
-      <c r="F53" s="286"/>
-      <c r="G53" s="287"/>
-      <c r="H53" s="267"/>
-      <c r="I53" s="268"/>
+      <c r="C53" s="206"/>
+      <c r="D53" s="207"/>
+      <c r="E53" s="207"/>
+      <c r="F53" s="207"/>
+      <c r="G53" s="208"/>
+      <c r="H53" s="209"/>
+      <c r="I53" s="210"/>
       <c r="J53" s="123"/>
       <c r="K53" s="123"/>
       <c r="L53" s="25"/>
@@ -5109,10 +5109,10 @@
       <c r="G54" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="H54" s="269" t="s">
+      <c r="H54" s="211" t="s">
         <v>78</v>
       </c>
-      <c r="I54" s="270"/>
+      <c r="I54" s="212"/>
       <c r="J54" s="142"/>
       <c r="K54" s="143"/>
       <c r="L54" s="25"/>
@@ -5154,12 +5154,12 @@
       <c r="A57" s="26"/>
       <c r="B57" s="145"/>
       <c r="C57" s="146"/>
-      <c r="D57" s="284"/>
-      <c r="E57" s="284"/>
+      <c r="D57" s="205"/>
+      <c r="E57" s="205"/>
       <c r="F57" s="147"/>
       <c r="G57" s="147"/>
-      <c r="H57" s="280"/>
-      <c r="I57" s="280"/>
+      <c r="H57" s="201"/>
+      <c r="I57" s="201"/>
       <c r="J57" s="147"/>
       <c r="K57" s="147"/>
       <c r="L57" s="25"/>
@@ -5183,10 +5183,10 @@
       <c r="G58" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="H58" s="183" t="s">
+      <c r="H58" s="280" t="s">
         <v>70</v>
       </c>
-      <c r="I58" s="183"/>
+      <c r="I58" s="280"/>
       <c r="J58" s="152"/>
       <c r="K58" s="153"/>
       <c r="L58" s="25"/>
@@ -5202,8 +5202,8 @@
       <c r="E59" s="152"/>
       <c r="F59" s="154"/>
       <c r="G59" s="153"/>
-      <c r="H59" s="289"/>
-      <c r="I59" s="289"/>
+      <c r="H59" s="190"/>
+      <c r="I59" s="190"/>
       <c r="J59" s="152"/>
       <c r="K59" s="152"/>
       <c r="L59" s="25"/>
@@ -5217,8 +5217,8 @@
       <c r="E60" s="156"/>
       <c r="F60" s="157"/>
       <c r="G60" s="157"/>
-      <c r="H60" s="290"/>
-      <c r="I60" s="290"/>
+      <c r="H60" s="191"/>
+      <c r="I60" s="191"/>
       <c r="J60" s="157"/>
       <c r="K60" s="157"/>
       <c r="L60" s="25"/>
@@ -5247,8 +5247,8 @@
       <c r="E62" s="47"/>
       <c r="F62" s="45"/>
       <c r="G62" s="45"/>
-      <c r="H62" s="291"/>
-      <c r="I62" s="291"/>
+      <c r="H62" s="192"/>
+      <c r="I62" s="192"/>
       <c r="J62" s="45"/>
       <c r="K62" s="45"/>
       <c r="L62" s="4"/>
@@ -5262,8 +5262,8 @@
       <c r="E63" s="47"/>
       <c r="F63" s="45"/>
       <c r="G63" s="45"/>
-      <c r="H63" s="291"/>
-      <c r="I63" s="291"/>
+      <c r="H63" s="192"/>
+      <c r="I63" s="192"/>
       <c r="J63" s="45"/>
       <c r="K63" s="45"/>
       <c r="L63" s="4"/>
@@ -5277,8 +5277,8 @@
       <c r="E64" s="52"/>
       <c r="F64" s="53"/>
       <c r="G64" s="53"/>
-      <c r="H64" s="292"/>
-      <c r="I64" s="293"/>
+      <c r="H64" s="193"/>
+      <c r="I64" s="194"/>
       <c r="J64" s="53"/>
       <c r="K64" s="64"/>
       <c r="L64" s="4"/>
@@ -5292,8 +5292,8 @@
       <c r="E65" s="66"/>
       <c r="F65" s="51"/>
       <c r="G65" s="51"/>
-      <c r="H65" s="294"/>
-      <c r="I65" s="294"/>
+      <c r="H65" s="195"/>
+      <c r="I65" s="195"/>
       <c r="J65" s="51"/>
       <c r="K65" s="51"/>
       <c r="L65" s="4"/>
@@ -5307,8 +5307,8 @@
       <c r="E66" s="66"/>
       <c r="F66" s="51"/>
       <c r="G66" s="51"/>
-      <c r="H66" s="295"/>
-      <c r="I66" s="295"/>
+      <c r="H66" s="196"/>
+      <c r="I66" s="196"/>
       <c r="J66" s="51"/>
       <c r="K66" s="51"/>
       <c r="L66" s="4"/>
@@ -5322,8 +5322,8 @@
       <c r="E67" s="47"/>
       <c r="F67" s="49"/>
       <c r="G67" s="49"/>
-      <c r="H67" s="296"/>
-      <c r="I67" s="296"/>
+      <c r="H67" s="197"/>
+      <c r="I67" s="197"/>
       <c r="J67" s="49"/>
       <c r="K67" s="49"/>
       <c r="L67" s="4"/>
@@ -5352,8 +5352,8 @@
       <c r="E69" s="47"/>
       <c r="F69" s="49"/>
       <c r="G69" s="49"/>
-      <c r="H69" s="297"/>
-      <c r="I69" s="298"/>
+      <c r="H69" s="198"/>
+      <c r="I69" s="199"/>
       <c r="J69" s="49"/>
       <c r="K69" s="49"/>
       <c r="L69" s="4"/>
@@ -5367,8 +5367,8 @@
       <c r="E70" s="47"/>
       <c r="F70" s="49"/>
       <c r="G70" s="49"/>
-      <c r="H70" s="297"/>
-      <c r="I70" s="298"/>
+      <c r="H70" s="198"/>
+      <c r="I70" s="199"/>
       <c r="J70" s="49"/>
       <c r="K70" s="49"/>
       <c r="L70" s="4"/>
@@ -5397,8 +5397,8 @@
       <c r="E72" s="73"/>
       <c r="F72" s="74"/>
       <c r="G72" s="48"/>
-      <c r="H72" s="299"/>
-      <c r="I72" s="299"/>
+      <c r="H72" s="200"/>
+      <c r="I72" s="200"/>
       <c r="J72" s="45"/>
       <c r="K72" s="51"/>
       <c r="L72" s="4"/>
@@ -5412,8 +5412,8 @@
       <c r="E73" s="76"/>
       <c r="F73" s="77"/>
       <c r="G73" s="51"/>
-      <c r="H73" s="288"/>
-      <c r="I73" s="288"/>
+      <c r="H73" s="189"/>
+      <c r="I73" s="189"/>
       <c r="J73" s="45"/>
       <c r="K73" s="45"/>
       <c r="L73" s="4"/>
@@ -5427,8 +5427,8 @@
       <c r="E74" s="79"/>
       <c r="F74" s="80"/>
       <c r="G74" s="80"/>
-      <c r="H74" s="302"/>
-      <c r="I74" s="302"/>
+      <c r="H74" s="185"/>
+      <c r="I74" s="185"/>
       <c r="J74" s="81"/>
       <c r="K74" s="81"/>
       <c r="L74" s="4"/>
@@ -5442,8 +5442,8 @@
       <c r="E75" s="83"/>
       <c r="F75" s="83"/>
       <c r="G75" s="83"/>
-      <c r="H75" s="303"/>
-      <c r="I75" s="304"/>
+      <c r="H75" s="186"/>
+      <c r="I75" s="187"/>
       <c r="J75" s="84"/>
       <c r="K75" s="83"/>
       <c r="L75" s="4"/>
@@ -5457,8 +5457,8 @@
       <c r="E76" s="43"/>
       <c r="F76" s="43"/>
       <c r="G76" s="43"/>
-      <c r="H76" s="300"/>
-      <c r="I76" s="301"/>
+      <c r="H76" s="183"/>
+      <c r="I76" s="184"/>
       <c r="J76" s="86"/>
       <c r="K76" s="43"/>
       <c r="L76" s="4"/>
@@ -5472,8 +5472,8 @@
       <c r="E77" s="49"/>
       <c r="F77" s="49"/>
       <c r="G77" s="49"/>
-      <c r="H77" s="305"/>
-      <c r="I77" s="305"/>
+      <c r="H77" s="188"/>
+      <c r="I77" s="188"/>
       <c r="J77" s="87"/>
       <c r="K77" s="49"/>
       <c r="L77" s="4"/>
@@ -5487,8 +5487,8 @@
       <c r="E78" s="43"/>
       <c r="F78" s="43"/>
       <c r="G78" s="43"/>
-      <c r="H78" s="300"/>
-      <c r="I78" s="301"/>
+      <c r="H78" s="183"/>
+      <c r="I78" s="184"/>
       <c r="J78" s="86"/>
       <c r="K78" s="89"/>
       <c r="L78" s="4"/>
@@ -5502,8 +5502,8 @@
       <c r="E79" s="43"/>
       <c r="F79" s="43"/>
       <c r="G79" s="43"/>
-      <c r="H79" s="300"/>
-      <c r="I79" s="301"/>
+      <c r="H79" s="183"/>
+      <c r="I79" s="184"/>
       <c r="J79" s="86"/>
       <c r="K79" s="89"/>
       <c r="L79" s="91"/>
@@ -5517,8 +5517,8 @@
       <c r="E80" s="43"/>
       <c r="F80" s="43"/>
       <c r="G80" s="43"/>
-      <c r="H80" s="300"/>
-      <c r="I80" s="301"/>
+      <c r="H80" s="183"/>
+      <c r="I80" s="184"/>
       <c r="J80" s="86"/>
       <c r="K80" s="89"/>
       <c r="L80" s="91"/>
@@ -5532,8 +5532,8 @@
       <c r="E81" s="43"/>
       <c r="F81" s="43"/>
       <c r="G81" s="43"/>
-      <c r="H81" s="300"/>
-      <c r="I81" s="301"/>
+      <c r="H81" s="183"/>
+      <c r="I81" s="184"/>
       <c r="J81" s="86"/>
       <c r="K81" s="89"/>
       <c r="L81" s="4"/>
@@ -5634,82 +5634,6 @@
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:K8"/>
     <mergeCell ref="H58:I58"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="H7:I7"/>
@@ -5726,6 +5650,82 @@
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H79:I79"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
